--- a/results/publication/Table3_replication_stage1_markers.xlsx
+++ b/results/publication/Table3_replication_stage1_markers.xlsx
@@ -189,19 +189,19 @@
     <t>0.2</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0.34</t>
-  </si>
-  <si>
-    <t>0.68</t>
-  </si>
-  <si>
-    <t>0.41</t>
-  </si>
-  <si>
-    <t>0.5</t>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>0.048</t>
+  </si>
+  <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>0.43</t>
   </si>
   <si>
     <t>no</t>
@@ -1496,7 +1496,7 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1690,13 +1690,13 @@
         <v>0.911689201645149</v>
       </c>
       <c r="Y2">
-        <v>-0.0063242338010189</v>
+        <v>-0.0770023011631777</v>
       </c>
       <c r="Z2">
-        <v>0.9968152255939304</v>
+        <v>0.9506914214317976</v>
       </c>
       <c r="AA2">
-        <v>0.4883708485316103</v>
+        <v>0.495386204495285</v>
       </c>
       <c r="AB2">
         <v>0.6093910434441951</v>
@@ -1797,13 +1797,13 @@
         <v>0.0001395190444079</v>
       </c>
       <c r="Y3">
-        <v>1.201457730989639</v>
+        <v>1.719028338527515</v>
       </c>
       <c r="Z3">
-        <v>0.3410775096158311</v>
+        <v>0.0481504764906196</v>
       </c>
       <c r="AA3">
-        <v>0.270148532728506</v>
+        <v>0.0041926228329791</v>
       </c>
       <c r="AB3">
         <v>0.0013972840233135</v>
@@ -1818,10 +1818,10 @@
         <v>1</v>
       </c>
       <c r="AF3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH3">
         <v>0.9777777777777776</v>
@@ -2107,13 +2107,13 @@
         <v>0.1659537788290849</v>
       </c>
       <c r="Y8">
-        <v>0.8668690664826162</v>
+        <v>0.5042462415408512</v>
       </c>
       <c r="Z8">
-        <v>0.6811769147247471</v>
+        <v>0.7357163646539461</v>
       </c>
       <c r="AA8">
-        <v>0.5632366271431426</v>
+        <v>0.2108118422350011</v>
       </c>
       <c r="AB8">
         <v>0.09422436158588041</v>
@@ -2214,13 +2214,13 @@
         <v>0.0353670690120257</v>
       </c>
       <c r="Y9">
-        <v>-1.256072898050909</v>
+        <v>-0.6834973524015671</v>
       </c>
       <c r="Z9">
-        <v>0.4108626538763745</v>
+        <v>0.5534427293685833</v>
       </c>
       <c r="AA9">
-        <v>0.2268047955085498</v>
+        <v>0.4764326983244137</v>
       </c>
       <c r="AB9">
         <v>0.1168255185525406</v>
@@ -2436,13 +2436,13 @@
         <v>0.2016693135918543</v>
       </c>
       <c r="Y12">
-        <v>1.465123538004964</v>
+        <v>1.163939197454799</v>
       </c>
       <c r="Z12">
-        <v>0.4988567247854298</v>
+        <v>0.4316140595930487</v>
       </c>
       <c r="AA12">
-        <v>0.3409871533819059</v>
+        <v>0.4643801294213285</v>
       </c>
       <c r="AB12">
         <v>0.5835252998336341</v>
